--- a/requirements/wealth-level/outputs/api-test-cases/api-test-cases.xlsx
+++ b/requirements/wealth-level/outputs/api-test-cases/api-test-cases.xlsx
@@ -18,34 +18,34 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>接口</t>
+          <t>描述</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>场景类型</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>覆盖权重</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>协议</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>方法</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>路径</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>测试维度</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>设计方法</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>等价类</t>
-        </is>
-      </c>
       <c r="H1" t="inlineStr">
         <is>
           <t>优先级</t>
@@ -53,2020 +53,7912 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>用例标题</t>
+          <t>标签</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>前置条件</t>
+          <t>依赖与变量</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>步骤</t>
+          <t>请求载荷</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>请求变异</t>
+          <t>协议断言</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>预期结果</t>
+          <t>Schema断言</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
+          <t>业务断言</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>数据断言</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>性能断言</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>清理</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>是否推断</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>需要复核</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>建议</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
           <t>推荐工具</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>自动化状态</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>安全策略</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>API-00001</t>
+          <t>TC_WEALTH_LEVEL_001_normal</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>获取财富等级经验及等级权益</t>
+          <t>获取财富等级经验及等级权益：有效等价类正常请求</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>/level/exeperience/v2/get</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>功能</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>等价类划分</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>valid</t>
-        </is>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>获取财富等级经验及等级权益：有效等价类正常请求</t>
+          <t>regression, normal, smoke, critical, exploratory</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>测试环境可用
-准备接口所需身份与公共参数
-确认测试数据可恢复或只读</t>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>按请求变异规则准备数据
-发送 GET /level/exeperience/v2/get
-检查HTTP状态、业务码、响应Schema和业务数据</t>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "use_valid_baseline", "exploratory_injection": {"field": "__debug", "value": true}}}</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>{"action": "use_valid_baseline"}</t>
+          <t>{"status": 200, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>返回成功状态，响应Schema及核心业务结果正确。</t>
+          <t>{"type": "object"}</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
+          <t>["返回成功状态，响应Schema及核心业务结果正确。"]</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
           <t>Newman</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>READY</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>STANDARD_TEST_ENVIRONMENT</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>API-00002</t>
+          <t>TC_WEALTH_LEVEL_002_normal</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>获取财富等级经验及等级权益</t>
+          <t>获取财富等级经验及等级权益：响应状态与Schema契约</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>/level/exeperience/v2/get</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>响应契约</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>契约校验</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>valid</t>
-        </is>
-      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>获取财富等级经验及等级权益：响应状态与Schema契约</t>
+          <t>regression, normal, smoke, critical, exploratory</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>测试环境可用
-准备接口所需身份与公共参数
-确认测试数据可恢复或只读</t>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>按请求变异规则准备数据
-发送 GET /level/exeperience/v2/get
-检查HTTP状态、业务码、响应Schema和业务数据</t>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "validate_response_contract", "exploratory_injection": {"field": "__debug", "value": true}}}</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>{"action": "validate_response_contract"}</t>
+          <t>{"status": 200, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>HTTP状态、业务码、必填响应字段、字段类型和枚举均符合OpenAPI契约，不泄露未声明敏感字段。</t>
+          <t>{"type": "object"}</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
+          <t>["HTTP状态、业务码、必填响应字段、字段类型和枚举均符合OpenAPI契约，不泄露未声明敏感字段。"]</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
           <t>Newman</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>READY</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>STANDARD_TEST_ENVIRONMENT</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>API-00003</t>
+          <t>TC_WEALTH_LEVEL_003_exception</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>获取财富等级经验及等级权益</t>
+          <t>获取财富等级经验及等级权益：使用不支持的HTTP方法</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>exception</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1.66666667</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>/level/exeperience/v2/get</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>异常处理</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>错误推测</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>invalid</t>
-        </is>
-      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>获取财富等级经验及等级权益：使用不支持的HTTP方法</t>
+          <t>regression, exception, exploratory</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>测试环境可用
-准备接口所需身份与公共参数
-确认测试数据可恢复或只读</t>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>按请求变异规则准备数据
-发送 GET /level/exeperience/v2/get
-检查HTTP状态、业务码、响应Schema和业务数据</t>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "use_unsupported_http_method", "exploratory_injection": {"field": "__debug", "value": true}}}</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>{"action": "use_unsupported_http_method"}</t>
+          <t>{"status": 405, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>返回405或明确的业务拒绝，不执行原接口业务写入。</t>
+          <t>{"type": "object"}</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
+          <t>["返回405或明确的业务拒绝，不执行原接口业务写入。"]</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
           <t>Newman</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>READY</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>STANDARD_TEST_ENVIRONMENT</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>API-00004</t>
+          <t>TC_WEALTH_LEVEL_004_exception</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>获取财富等级经验及等级权益</t>
+          <t>获取财富等级经验及等级权益：缺失必填字段 query.ticket</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>exception</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1.66666667</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>/level/exeperience/v2/get</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>参数校验</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>等价类划分</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>invalid</t>
-        </is>
-      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>获取财富等级经验及等级权益：缺失必填字段 query.ticket</t>
+          <t>regression, exception, critical, exploratory</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>测试环境可用
-准备接口所需身份与公共参数
-确认测试数据可恢复或只读</t>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>按请求变异规则准备数据
-发送 GET /level/exeperience/v2/get
-检查HTTP状态、业务码、响应Schema和业务数据</t>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "remove", "field": "query.ticket", "exploratory_injection": {"field": "__debug", "value": true}}}</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>{"action": "remove", "field": "query.ticket"}</t>
+          <t>{"status": 400, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>接口明确拒绝请求，不产生错误业务数据。</t>
+          <t>{"type": "object"}</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
+          <t>["接口明确拒绝请求，不产生错误业务数据。"]</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
           <t>Newman</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>READY</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>STANDARD_TEST_ENVIRONMENT</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>API-00005</t>
+          <t>TC_WEALTH_LEVEL_005_exception</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>获取财富等级经验及等级权益</t>
+          <t>获取财富等级经验及等级权益：query.ticket 非法null</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>exception</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1.66666667</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>/level/exeperience/v2/get</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>参数校验</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>等价类划分</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>invalid</t>
-        </is>
-      </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>获取财富等级经验及等级权益：query.ticket 非法null</t>
+          <t>regression, exception, exploratory</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>测试环境可用
-准备接口所需身份与公共参数
-确认测试数据可恢复或只读</t>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>按请求变异规则准备数据
-发送 GET /level/exeperience/v2/get
-检查HTTP状态、业务码、响应Schema和业务数据</t>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "replace", "field": "query.ticket", "value": null, "exploratory_injection": {"field": "__debug", "value": true}}}</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>{"action": "replace", "field": "query.ticket", "value": null}</t>
+          <t>{"status": 400, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>接口拒绝必填且不可为空字段的null值，不产生500或脏数据。</t>
+          <t>{"type": "object"}</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
+          <t>["接口拒绝必填且不可为空字段的null值，不产生500或脏数据。"]</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
           <t>Newman</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>READY</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>STANDARD_TEST_ENVIRONMENT</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>API-00006</t>
+          <t>TC_WEALTH_LEVEL_006_boundary</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>获取财富等级经验及等级权益</t>
+          <t>获取财富等级经验及等级权益：query.ticket 空值边界</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>boundary</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0.45454545</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>/level/exeperience/v2/get</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>边界值</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>边界值分析</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>invalid</t>
-        </is>
-      </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>获取财富等级经验及等级权益：query.ticket 空值边界</t>
+          <t>regression, boundary</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>测试环境可用
-准备接口所需身份与公共参数
-确认测试数据可恢复或只读</t>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>按请求变异规则准备数据
-发送 GET /level/exeperience/v2/get
-检查HTTP状态、业务码、响应Schema和业务数据</t>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "replace", "field": "query.ticket", "value": ""}}</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>{"action": "replace", "field": "query.ticket", "value": ""}</t>
+          <t>{"status": 400, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>接口按Schema和业务规则接受或明确拒绝，不能产生500。</t>
+          <t>{"type": "object"}</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
+          <t>["接口按Schema和业务规则接受或明确拒绝，不能产生500。"]</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
           <t>Newman</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>READY</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>STANDARD_TEST_ENVIRONMENT</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>API-00007</t>
+          <t>TC_WEALTH_LEVEL_007_exception</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>获取财富等级经验及等级权益</t>
+          <t>获取财富等级经验及等级权益：query.ticket 类型错误</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>exception</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1.66666667</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>/level/exeperience/v2/get</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>参数校验</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>等价类划分</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>invalid</t>
-        </is>
-      </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>获取财富等级经验及等级权益：query.ticket 类型错误</t>
+          <t>regression, exception, exploratory</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>测试环境可用
-准备接口所需身份与公共参数
-确认测试数据可恢复或只读</t>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>按请求变异规则准备数据
-发送 GET /level/exeperience/v2/get
-检查HTTP状态、业务码、响应Schema和业务数据</t>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "replace", "field": "query.ticket", "value": 123456, "expected_type": "string", "exploratory_injection": {"field": "__debug", "value": true}}}</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>{"action": "replace", "field": "query.ticket", "value": 123456, "expected_type": "string"}</t>
+          <t>{"status": 400, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>接口返回参数错误，不产生500和业务脏数据。</t>
+          <t>{"type": "object"}</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
+          <t>["接口返回参数错误，不产生500和业务脏数据。"]</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
           <t>Newman</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>READY</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>STANDARD_TEST_ENVIRONMENT</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>API-00008</t>
+          <t>TC_WEALTH_LEVEL_008_boundary</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>获取财富等级经验及等级权益</t>
+          <t>获取财富等级经验及等级权益：query.ticket minLength-1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>boundary</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0.45454545</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>/level/exeperience/v2/get</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>参数校验</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>等价类划分</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>invalid</t>
-        </is>
-      </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>获取财富等级经验及等级权益：缺失必填字段 query.uid</t>
+          <t>regression, boundary</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>测试环境可用
-准备接口所需身份与公共参数
-确认测试数据可恢复或只读</t>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>按请求变异规则准备数据
-发送 GET /level/exeperience/v2/get
-检查HTTP状态、业务码、响应Schema和业务数据</t>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "replace", "field": "query.ticket", "value": "", "boundary": "minLength-1"}}</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>{"action": "remove", "field": "query.uid"}</t>
+          <t>{"status": 400, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>接口明确拒绝请求，不产生错误业务数据。</t>
+          <t>{"type": "object"}</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
+          <t>["边界归属符合Schema；越界值被拒绝且不产生500。"]</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
           <t>Newman</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>READY</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>STANDARD_TEST_ENVIRONMENT</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>API-00009</t>
+          <t>TC_WEALTH_LEVEL_009_boundary</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>获取财富等级经验及等级权益</t>
+          <t>获取财富等级经验及等级权益：query.ticket minLength</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>boundary</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>0.45454545</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>/level/exeperience/v2/get</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>参数校验</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>等价类划分</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>invalid</t>
-        </is>
-      </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>获取财富等级经验及等级权益：query.uid 非法null</t>
+          <t>regression, boundary</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>测试环境可用
-准备接口所需身份与公共参数
-确认测试数据可恢复或只读</t>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>按请求变异规则准备数据
-发送 GET /level/exeperience/v2/get
-检查HTTP状态、业务码、响应Schema和业务数据</t>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "replace", "field": "query.ticket", "value": "a", "boundary": "minLength"}}</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>{"action": "replace", "field": "query.uid", "value": null}</t>
+          <t>{"status": 400, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>接口拒绝必填且不可为空字段的null值，不产生500或脏数据。</t>
+          <t>{"type": "object"}</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
+          <t>["边界归属符合Schema；越界值被拒绝且不产生500。"]</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
           <t>Newman</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>READY</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>STANDARD_TEST_ENVIRONMENT</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>API-00010</t>
+          <t>TC_WEALTH_LEVEL_010_boundary</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>获取财富等级经验及等级权益</t>
+          <t>获取财富等级经验及等级权益：query.ticket minLength+1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>boundary</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>0.45454545</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>/level/exeperience/v2/get</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>边界值</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>边界值分析</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>invalid</t>
-        </is>
-      </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>获取财富等级经验及等级权益：query.uid 空值边界</t>
+          <t>regression, boundary</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>测试环境可用
-准备接口所需身份与公共参数
-确认测试数据可恢复或只读</t>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>按请求变异规则准备数据
-发送 GET /level/exeperience/v2/get
-检查HTTP状态、业务码、响应Schema和业务数据</t>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "replace", "field": "query.ticket", "value": "aa", "boundary": "minLength+1"}}</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>{"action": "replace", "field": "query.uid", "value": ""}</t>
+          <t>{"status": 400, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>接口按Schema和业务规则接受或明确拒绝，不能产生500。</t>
+          <t>{"type": "object"}</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
+          <t>["边界归属符合Schema；越界值被拒绝且不产生500。"]</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
           <t>Newman</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>READY</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>STANDARD_TEST_ENVIRONMENT</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>API-00011</t>
+          <t>TC_WEALTH_LEVEL_011_boundary</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>获取财富等级经验及等级权益</t>
+          <t>获取财富等级经验及等级权益：query.ticket maxLength-1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>boundary</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>0.45454545</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>/level/exeperience/v2/get</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>参数校验</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>等价类划分</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>invalid</t>
-        </is>
-      </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>获取财富等级经验及等级权益：query.uid 类型错误</t>
+          <t>regression, boundary</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>测试环境可用
-准备接口所需身份与公共参数
-确认测试数据可恢复或只读</t>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>按请求变异规则准备数据
-发送 GET /level/exeperience/v2/get
-检查HTTP状态、业务码、响应Schema和业务数据</t>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "replace", "field": "query.ticket", "value": "aaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaa", "boundary": "maxLength-1"}}</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>{"action": "replace", "field": "query.uid", "value": 123456, "expected_type": "string"}</t>
+          <t>{"status": 400, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>接口返回参数错误，不产生500和业务脏数据。</t>
+          <t>{"type": "object"}</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
+          <t>["边界归属符合Schema；越界值被拒绝且不产生500。"]</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
           <t>Newman</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>READY</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>STANDARD_TEST_ENVIRONMENT</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>API-00012</t>
+          <t>TC_WEALTH_LEVEL_012_boundary</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>获取财富等级经验及等级权益</t>
+          <t>获取财富等级经验及等级权益：query.ticket maxLength</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>boundary</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>0.45454545</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>/level/exeperience/v2/get</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>安全</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>攻击输入</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>invalid</t>
-        </is>
-      </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>获取财富等级经验及等级权益：query.uid SQL注入字符</t>
+          <t>regression, boundary</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>测试环境可用
-准备接口所需身份与公共参数
-确认测试数据可恢复或只读</t>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>按请求变异规则准备数据
-发送 GET /level/exeperience/v2/get
-检查HTTP状态、业务码、响应Schema和业务数据</t>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "replace", "field": "query.ticket", "value": "aaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaa", "boundary": "maxLength"}}</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>{"action": "replace", "field": "query.uid", "value": "' OR '1'='1' --"}</t>
+          <t>{"status": 400, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>接口不执行注入语义，不泄露数据库错误，不绕过鉴权或条件。</t>
+          <t>{"type": "object"}</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>pytest</t>
+          <t>["边界归属符合Schema；越界值被拒绝且不产生500。"]</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>{"db": null, "cache": null, "message": null}</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>ISOLATED_TEST_ENVIRONMENT_ONLY</t>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Newman</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>READY</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>API-00013</t>
+          <t>TC_WEALTH_LEVEL_013_boundary</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>获取财富等级经验及等级权益</t>
+          <t>获取财富等级经验及等级权益：query.ticket maxLength+1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>boundary</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0.45454545</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>/level/exeperience/v2/get</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>安全</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>攻击输入</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>invalid</t>
-        </is>
-      </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>获取财富等级经验及等级权益：query.uid XSS脚本字符</t>
+          <t>regression, boundary</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>测试环境可用
-准备接口所需身份与公共参数
-确认测试数据可恢复或只读</t>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>按请求变异规则准备数据
-发送 GET /level/exeperience/v2/get
-检查HTTP状态、业务码、响应Schema和业务数据</t>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "replace", "field": "query.ticket", "value": "aaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaa", "boundary": "maxLength+1"}}</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>{"action": "replace", "field": "query.uid", "value": "&lt;script&gt;alert(1)&lt;/script&gt;"}</t>
+          <t>{"status": 400, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>响应和持久化数据不得执行脚本，输出应安全编码。</t>
+          <t>{"type": "object"}</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>pytest</t>
+          <t>["边界归属符合Schema；越界值被拒绝且不产生500。"]</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>{"db": null, "cache": null, "message": null}</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>ISOLATED_TEST_ENVIRONMENT_ONLY</t>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Newman</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>READY</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>API-00014</t>
+          <t>TC_WEALTH_LEVEL_014_exception</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>获取财富等级经验及等级权益</t>
+          <t>获取财富等级经验及等级权益：缺失必填字段 query.uid</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>exception</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1.66666667</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>/level/exeperience/v2/get</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>边界值</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>边界值分析</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>boundary</t>
-        </is>
-      </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>获取财富等级经验及等级权益：query.language 空值边界</t>
+          <t>regression, exception, critical, exploratory</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>测试环境可用
-准备接口所需身份与公共参数
-确认测试数据可恢复或只读</t>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>按请求变异规则准备数据
-发送 GET /level/exeperience/v2/get
-检查HTTP状态、业务码、响应Schema和业务数据</t>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "remove", "field": "query.uid", "exploratory_injection": {"field": "__debug", "value": true}}}</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>{"action": "replace", "field": "query.language", "value": ""}</t>
+          <t>{"status": 400, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>接口按Schema和业务规则接受或明确拒绝，不能产生500。</t>
+          <t>{"type": "object"}</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
+          <t>["接口明确拒绝请求，不产生错误业务数据。"]</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
           <t>Newman</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>READY</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>STANDARD_TEST_ENVIRONMENT</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>API-00015</t>
+          <t>TC_WEALTH_LEVEL_015_exception</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>获取财富等级经验及等级权益</t>
+          <t>获取财富等级经验及等级权益：query.uid 非法null</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>exception</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1.66666667</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>/level/exeperience/v2/get</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>参数校验</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>等价类划分</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>invalid</t>
-        </is>
-      </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>获取财富等级经验及等级权益：query.language 类型错误</t>
+          <t>regression, exception, exploratory</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>测试环境可用
-准备接口所需身份与公共参数
-确认测试数据可恢复或只读</t>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>按请求变异规则准备数据
-发送 GET /level/exeperience/v2/get
-检查HTTP状态、业务码、响应Schema和业务数据</t>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "replace", "field": "query.uid", "value": null, "exploratory_injection": {"field": "__debug", "value": true}}}</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>{"action": "replace", "field": "query.language", "value": 123456, "expected_type": "string"}</t>
+          <t>{"status": 400, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>接口返回参数错误，不产生500和业务脏数据。</t>
+          <t>{"type": "object"}</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
+          <t>["接口拒绝必填且不可为空字段的null值，不产生500或脏数据。"]</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
           <t>Newman</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>READY</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>STANDARD_TEST_ENVIRONMENT</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>API-00016</t>
+          <t>TC_WEALTH_LEVEL_016_boundary</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>获取财富等级经验及等级权益</t>
+          <t>获取财富等级经验及等级权益：query.uid 空值边界</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>boundary</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>0.45454545</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>/level/exeperience/v2/get</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>边界值</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>边界值分析</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>boundary</t>
-        </is>
-      </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>获取财富等级经验及等级权益：query.systemLanguage 空值边界</t>
+          <t>regression, boundary</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>测试环境可用
-准备接口所需身份与公共参数
-确认测试数据可恢复或只读</t>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>按请求变异规则准备数据
-发送 GET /level/exeperience/v2/get
-检查HTTP状态、业务码、响应Schema和业务数据</t>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "replace", "field": "query.uid", "value": ""}}</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>{"action": "replace", "field": "query.systemLanguage", "value": ""}</t>
+          <t>{"status": 400, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>接口按Schema和业务规则接受或明确拒绝，不能产生500。</t>
+          <t>{"type": "object"}</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
+          <t>["接口按Schema和业务规则接受或明确拒绝，不能产生500。"]</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
           <t>Newman</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>READY</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>STANDARD_TEST_ENVIRONMENT</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>API-00017</t>
+          <t>TC_WEALTH_LEVEL_017_exception</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>获取财富等级经验及等级权益</t>
+          <t>获取财富等级经验及等级权益：query.uid 类型错误</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>exception</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1.66666667</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>/level/exeperience/v2/get</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>参数校验</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>等价类划分</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>invalid</t>
-        </is>
-      </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>获取财富等级经验及等级权益：query.systemLanguage 类型错误</t>
+          <t>regression, exception, exploratory</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>测试环境可用
-准备接口所需身份与公共参数
-确认测试数据可恢复或只读</t>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>按请求变异规则准备数据
-发送 GET /level/exeperience/v2/get
-检查HTTP状态、业务码、响应Schema和业务数据</t>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "replace", "field": "query.uid", "value": 123456, "expected_type": "string", "exploratory_injection": {"field": "__debug", "value": true}}}</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>{"action": "replace", "field": "query.systemLanguage", "value": 123456, "expected_type": "string"}</t>
+          <t>{"status": 400, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>接口返回参数错误，不产生500和业务脏数据。</t>
+          <t>{"type": "object"}</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
+          <t>["接口返回参数错误，不产生500和业务脏数据。"]</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
           <t>Newman</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>READY</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>STANDARD_TEST_ENVIRONMENT</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>API-00018</t>
+          <t>TC_WEALTH_LEVEL_018_boundary</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>获取财富等级经验及等级权益</t>
+          <t>获取财富等级经验及等级权益：query.uid minLength-1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>boundary</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0.45454545</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>/level/exeperience/v2/get</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>边界值</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>边界值分析</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>boundary</t>
-        </is>
-      </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>获取财富等级经验及等级权益：query.appVersion 空值边界</t>
+          <t>regression, boundary</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>测试环境可用
-准备接口所需身份与公共参数
-确认测试数据可恢复或只读</t>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>按请求变异规则准备数据
-发送 GET /level/exeperience/v2/get
-检查HTTP状态、业务码、响应Schema和业务数据</t>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "replace", "field": "query.uid", "value": "", "boundary": "minLength-1"}}</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>{"action": "replace", "field": "query.appVersion", "value": ""}</t>
+          <t>{"status": 400, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>接口按Schema和业务规则接受或明确拒绝，不能产生500。</t>
+          <t>{"type": "object"}</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
+          <t>["边界归属符合Schema；越界值被拒绝且不产生500。"]</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
           <t>Newman</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>READY</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>STANDARD_TEST_ENVIRONMENT</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>API-00019</t>
+          <t>TC_WEALTH_LEVEL_019_boundary</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>获取财富等级经验及等级权益</t>
+          <t>获取财富等级经验及等级权益：query.uid minLength</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>boundary</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>0.45454545</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>/level/exeperience/v2/get</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>参数校验</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>等价类划分</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>invalid</t>
-        </is>
-      </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>获取财富等级经验及等级权益：query.appVersion 类型错误</t>
+          <t>regression, boundary</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>测试环境可用
-准备接口所需身份与公共参数
-确认测试数据可恢复或只读</t>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>按请求变异规则准备数据
-发送 GET /level/exeperience/v2/get
-检查HTTP状态、业务码、响应Schema和业务数据</t>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "replace", "field": "query.uid", "value": "a", "boundary": "minLength"}}</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>{"action": "replace", "field": "query.appVersion", "value": 123456, "expected_type": "string"}</t>
+          <t>{"status": 400, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>接口返回参数错误，不产生500和业务脏数据。</t>
+          <t>{"type": "object"}</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
+          <t>["边界归属符合Schema；越界值被拒绝且不产生500。"]</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
           <t>Newman</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>READY</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>STANDARD_TEST_ENVIRONMENT</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>API-00020</t>
+          <t>TC_WEALTH_LEVEL_020_boundary</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>获取财富等级经验及等级权益</t>
+          <t>获取财富等级经验及等级权益：query.uid minLength+1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>boundary</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>0.45454545</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>/level/exeperience/v2/get</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>边界值</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>边界值分析</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>boundary</t>
-        </is>
-      </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>获取财富等级经验及等级权益：query.deviceType 空值边界</t>
+          <t>regression, boundary</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>测试环境可用
-准备接口所需身份与公共参数
-确认测试数据可恢复或只读</t>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>按请求变异规则准备数据
-发送 GET /level/exeperience/v2/get
-检查HTTP状态、业务码、响应Schema和业务数据</t>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "replace", "field": "query.uid", "value": "aa", "boundary": "minLength+1"}}</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>{"action": "replace", "field": "query.deviceType", "value": ""}</t>
+          <t>{"status": 400, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>接口按Schema和业务规则接受或明确拒绝，不能产生500。</t>
+          <t>{"type": "object"}</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
+          <t>["边界归属符合Schema；越界值被拒绝且不产生500。"]</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
           <t>Newman</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>READY</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>STANDARD_TEST_ENVIRONMENT</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>API-00021</t>
+          <t>TC_WEALTH_LEVEL_021_boundary</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>获取财富等级经验及等级权益</t>
+          <t>获取财富等级经验及等级权益：query.uid maxLength-1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
+          <t>boundary</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>0.45454545</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>/level/exeperience/v2/get</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>参数校验</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>等价类划分</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>invalid</t>
-        </is>
-      </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>获取财富等级经验及等级权益：query.deviceType 类型错误</t>
+          <t>regression, boundary</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>测试环境可用
-准备接口所需身份与公共参数
-确认测试数据可恢复或只读</t>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>按请求变异规则准备数据
-发送 GET /level/exeperience/v2/get
-检查HTTP状态、业务码、响应Schema和业务数据</t>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "replace", "field": "query.uid", "value": "aaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaa", "boundary": "maxLength-1"}}</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>{"action": "replace", "field": "query.deviceType", "value": 123456, "expected_type": "string"}</t>
+          <t>{"status": 400, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>接口返回参数错误，不产生500和业务脏数据。</t>
+          <t>{"type": "object"}</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
+          <t>["边界归属符合Schema；越界值被拒绝且不产生500。"]</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
           <t>Newman</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>READY</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>STANDARD_TEST_ENVIRONMENT</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>API-00022</t>
+          <t>TC_WEALTH_LEVEL_022_boundary</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>获取财富等级经验及等级权益</t>
+          <t>获取财富等级经验及等级权益：query.uid maxLength</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>boundary</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>0.45454545</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>/level/exeperience/v2/get</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>认证授权</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>等价类划分</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>invalid</t>
-        </is>
-      </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>获取财富等级经验及等级权益：缺失认证凭证</t>
+          <t>regression, boundary</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>测试环境可用
-准备接口所需身份与公共参数
-确认测试数据可恢复或只读</t>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>按请求变异规则准备数据
-发送 GET /level/exeperience/v2/get
-检查HTTP状态、业务码、响应Schema和业务数据</t>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "replace", "field": "query.uid", "value": "aaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaa", "boundary": "maxLength"}}</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>{"action": "remove_auth"}</t>
+          <t>{"status": 400, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>返回401或403，不返回受保护业务数据。</t>
+          <t>{"type": "object"}</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
+          <t>["边界归属符合Schema；越界值被拒绝且不产生500。"]</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
           <t>Newman</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>READY</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>STANDARD_TEST_ENVIRONMENT</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>API-00023</t>
+          <t>TC_WEALTH_LEVEL_023_boundary</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>获取财富等级经验及等级权益</t>
+          <t>获取财富等级经验及等级权益：query.uid maxLength+1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
+          <t>boundary</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>0.45454545</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>/level/exeperience/v2/get</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>认证授权</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>等价类划分</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>invalid</t>
-        </is>
-      </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
+          <t>regression, boundary</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "replace", "field": "query.uid", "value": "aaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaa", "boundary": "maxLength+1"}}</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>{"status": 400, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>{"type": "object"}</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>["边界归属符合Schema；越界值被拒绝且不产生500。"]</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Newman</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>TC_WEALTH_LEVEL_024_exception</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>获取财富等级经验及等级权益：query.uid SQL注入字符</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>exception</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>1.66666667</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>/level/exeperience/v2/get</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>critical</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>regression, exception, critical, security</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "replace", "field": "query.uid", "value": "' OR '1'='1' --"}}</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>{"status": 400, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>{"type": "object"}</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>["接口不执行注入语义，不泄露数据库错误，不绕过鉴权或条件。"]</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>pytest</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>REVIEW_REQUIRED</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>TC_WEALTH_LEVEL_025_exception</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>获取财富等级经验及等级权益：query.uid XSS脚本字符</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>exception</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>1.66666667</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>/level/exeperience/v2/get</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>regression, exception, security</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "replace", "field": "query.uid", "value": "&lt;script&gt;alert(1)&lt;/script&gt;"}}</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>{"status": 400, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>{"type": "object"}</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>["响应和持久化数据不得执行脚本，输出应安全编码。"]</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>pytest</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>REVIEW_REQUIRED</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>TC_WEALTH_LEVEL_026_boundary</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>获取财富等级经验及等级权益：query.language 空值边界</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>boundary</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>0.45454545</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>/level/exeperience/v2/get</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>regression, boundary</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "replace", "field": "query.language", "value": ""}}</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>{"status": 400, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>{"type": "object"}</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>["接口按Schema和业务规则接受或明确拒绝，不能产生500。"]</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Newman</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>TC_WEALTH_LEVEL_027_exception</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>获取财富等级经验及等级权益：query.language 类型错误</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>exception</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>1.66666667</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>/level/exeperience/v2/get</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>regression, exception, exploratory</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "replace", "field": "query.language", "value": 123456, "expected_type": "string", "exploratory_injection": {"field": "__debug", "value": true}}}</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>{"status": 400, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>{"type": "object"}</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>["接口返回参数错误，不产生500和业务脏数据。"]</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Newman</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>TC_WEALTH_LEVEL_028_boundary</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>获取财富等级经验及等级权益：query.language minLength-1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>boundary</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>0.45454545</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>/level/exeperience/v2/get</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>regression, boundary</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "replace", "field": "query.language", "value": "", "boundary": "minLength-1"}}</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>{"status": 400, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>{"type": "object"}</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>["边界归属符合Schema；越界值被拒绝且不产生500。"]</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Newman</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>TC_WEALTH_LEVEL_029_boundary</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>获取财富等级经验及等级权益：query.language minLength</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>boundary</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>0.45454545</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>/level/exeperience/v2/get</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>regression, boundary</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "replace", "field": "query.language", "value": "a", "boundary": "minLength"}}</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>{"status": 400, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>{"type": "object"}</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>["边界归属符合Schema；越界值被拒绝且不产生500。"]</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Newman</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>TC_WEALTH_LEVEL_030_boundary</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>获取财富等级经验及等级权益：query.language minLength+1</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>boundary</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>0.45454545</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>/level/exeperience/v2/get</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>regression, boundary</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "replace", "field": "query.language", "value": "aa", "boundary": "minLength+1"}}</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>{"status": 400, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>{"type": "object"}</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>["边界归属符合Schema；越界值被拒绝且不产生500。"]</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Newman</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>TC_WEALTH_LEVEL_031_boundary</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>获取财富等级经验及等级权益：query.language maxLength-1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>boundary</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>0.45454545</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>/level/exeperience/v2/get</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>regression, boundary</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "replace", "field": "query.language", "value": "aaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaa", "boundary": "maxLength-1"}}</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>{"status": 400, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>{"type": "object"}</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>["边界归属符合Schema；越界值被拒绝且不产生500。"]</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Newman</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>TC_WEALTH_LEVEL_032_boundary</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>获取财富等级经验及等级权益：query.language maxLength</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>boundary</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>0.45454545</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>/level/exeperience/v2/get</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>regression, boundary</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "replace", "field": "query.language", "value": "aaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaa", "boundary": "maxLength"}}</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>{"status": 400, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>{"type": "object"}</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>["边界归属符合Schema；越界值被拒绝且不产生500。"]</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Newman</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>TC_WEALTH_LEVEL_033_boundary</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>获取财富等级经验及等级权益：query.language maxLength+1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>boundary</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>0.45454545</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>/level/exeperience/v2/get</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>regression, boundary</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "replace", "field": "query.language", "value": "aaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaa", "boundary": "maxLength+1"}}</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>{"status": 400, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>{"type": "object"}</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>["边界归属符合Schema；越界值被拒绝且不产生500。"]</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Newman</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>TC_WEALTH_LEVEL_034_boundary</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>获取财富等级经验及等级权益：query.systemLanguage 空值边界</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>boundary</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>0.45454545</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>/level/exeperience/v2/get</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>regression, boundary</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "replace", "field": "query.systemLanguage", "value": ""}}</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>{"status": 400, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>{"type": "object"}</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>["接口按Schema和业务规则接受或明确拒绝，不能产生500。"]</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Newman</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>TC_WEALTH_LEVEL_035_exception</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>获取财富等级经验及等级权益：query.systemLanguage 类型错误</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>exception</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>1.66666667</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>/level/exeperience/v2/get</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>regression, exception, exploratory</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "replace", "field": "query.systemLanguage", "value": 123456, "expected_type": "string", "exploratory_injection": {"field": "__debug", "value": true}}}</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>{"status": 400, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>{"type": "object"}</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>["接口返回参数错误，不产生500和业务脏数据。"]</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Newman</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>TC_WEALTH_LEVEL_036_boundary</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>获取财富等级经验及等级权益：query.systemLanguage minLength-1</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>boundary</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>0.45454545</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>/level/exeperience/v2/get</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>regression, boundary</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "replace", "field": "query.systemLanguage", "value": "", "boundary": "minLength-1"}}</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>{"status": 400, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>{"type": "object"}</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>["边界归属符合Schema；越界值被拒绝且不产生500。"]</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Newman</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>TC_WEALTH_LEVEL_037_boundary</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>获取财富等级经验及等级权益：query.systemLanguage minLength</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>boundary</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>0.45454545</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>/level/exeperience/v2/get</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>regression, boundary</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "replace", "field": "query.systemLanguage", "value": "a", "boundary": "minLength"}}</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>{"status": 400, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>{"type": "object"}</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>["边界归属符合Schema；越界值被拒绝且不产生500。"]</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Newman</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>TC_WEALTH_LEVEL_038_boundary</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>获取财富等级经验及等级权益：query.systemLanguage minLength+1</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>boundary</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>0.45454545</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>/level/exeperience/v2/get</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>regression, boundary</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "replace", "field": "query.systemLanguage", "value": "aa", "boundary": "minLength+1"}}</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>{"status": 400, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>{"type": "object"}</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>["边界归属符合Schema；越界值被拒绝且不产生500。"]</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Newman</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>TC_WEALTH_LEVEL_039_boundary</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>获取财富等级经验及等级权益：query.systemLanguage maxLength-1</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>boundary</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>0.45454545</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>/level/exeperience/v2/get</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>regression, boundary</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "replace", "field": "query.systemLanguage", "value": "aaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaa", "boundary": "maxLength-1"}}</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>{"status": 400, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>{"type": "object"}</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>["边界归属符合Schema；越界值被拒绝且不产生500。"]</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Newman</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>TC_WEALTH_LEVEL_040_boundary</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>获取财富等级经验及等级权益：query.systemLanguage maxLength</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>boundary</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>0.45454545</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>/level/exeperience/v2/get</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>regression, boundary</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "replace", "field": "query.systemLanguage", "value": "aaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaa", "boundary": "maxLength"}}</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>{"status": 400, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>{"type": "object"}</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>["边界归属符合Schema；越界值被拒绝且不产生500。"]</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Newman</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>TC_WEALTH_LEVEL_041_boundary</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>获取财富等级经验及等级权益：query.systemLanguage maxLength+1</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>boundary</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>0.45454545</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>/level/exeperience/v2/get</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>regression, boundary</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "replace", "field": "query.systemLanguage", "value": "aaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaa", "boundary": "maxLength+1"}}</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>{"status": 400, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>{"type": "object"}</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>["边界归属符合Schema；越界值被拒绝且不产生500。"]</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Newman</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>TC_WEALTH_LEVEL_042_boundary</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>获取财富等级经验及等级权益：query.appVersion 空值边界</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>boundary</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>0.45454545</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>/level/exeperience/v2/get</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>regression, boundary</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "replace", "field": "query.appVersion", "value": ""}}</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>{"status": 400, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>{"type": "object"}</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>["接口按Schema和业务规则接受或明确拒绝，不能产生500。"]</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Newman</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>TC_WEALTH_LEVEL_043_exception</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>获取财富等级经验及等级权益：query.appVersion 类型错误</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>exception</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1.66666667</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>/level/exeperience/v2/get</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>regression, exception, exploratory</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "replace", "field": "query.appVersion", "value": 123456, "expected_type": "string", "exploratory_injection": {"field": "__debug", "value": true}}}</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>{"status": 400, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>{"type": "object"}</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>["接口返回参数错误，不产生500和业务脏数据。"]</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Newman</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>TC_WEALTH_LEVEL_044_boundary</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>获取财富等级经验及等级权益：query.appVersion minLength-1</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>boundary</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>0.45454545</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>/level/exeperience/v2/get</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>regression, boundary</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "replace", "field": "query.appVersion", "value": "", "boundary": "minLength-1"}}</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>{"status": 400, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>{"type": "object"}</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>["边界归属符合Schema；越界值被拒绝且不产生500。"]</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Newman</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>TC_WEALTH_LEVEL_045_boundary</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>获取财富等级经验及等级权益：query.appVersion minLength</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>boundary</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>0.45454545</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>/level/exeperience/v2/get</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>regression, boundary</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "replace", "field": "query.appVersion", "value": "a", "boundary": "minLength"}}</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>{"status": 400, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>{"type": "object"}</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>["边界归属符合Schema；越界值被拒绝且不产生500。"]</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Newman</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>TC_WEALTH_LEVEL_046_boundary</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>获取财富等级经验及等级权益：query.appVersion minLength+1</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>boundary</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.45454545</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>/level/exeperience/v2/get</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>regression, boundary</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "replace", "field": "query.appVersion", "value": "aa", "boundary": "minLength+1"}}</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>{"status": 400, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>{"type": "object"}</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>["边界归属符合Schema；越界值被拒绝且不产生500。"]</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Newman</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>TC_WEALTH_LEVEL_047_boundary</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>获取财富等级经验及等级权益：query.appVersion maxLength-1</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>boundary</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.45454545</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>/level/exeperience/v2/get</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>regression, boundary</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "replace", "field": "query.appVersion", "value": "aaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaa", "boundary": "maxLength-1"}}</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>{"status": 400, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>{"type": "object"}</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>["边界归属符合Schema；越界值被拒绝且不产生500。"]</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Newman</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>TC_WEALTH_LEVEL_048_boundary</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>获取财富等级经验及等级权益：query.appVersion maxLength</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>boundary</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.45454545</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>/level/exeperience/v2/get</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>regression, boundary</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "replace", "field": "query.appVersion", "value": "aaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaa", "boundary": "maxLength"}}</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>{"status": 400, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>{"type": "object"}</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>["边界归属符合Schema；越界值被拒绝且不产生500。"]</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Newman</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>TC_WEALTH_LEVEL_049_boundary</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>获取财富等级经验及等级权益：query.appVersion maxLength+1</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>boundary</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.45454545</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>/level/exeperience/v2/get</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>regression, boundary</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "replace", "field": "query.appVersion", "value": "aaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaa", "boundary": "maxLength+1"}}</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>{"status": 400, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>{"type": "object"}</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>["边界归属符合Schema；越界值被拒绝且不产生500。"]</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Newman</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>TC_WEALTH_LEVEL_050_boundary</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>获取财富等级经验及等级权益：query.deviceType 空值边界</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>boundary</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.45454545</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>/level/exeperience/v2/get</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>regression, boundary</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "replace", "field": "query.deviceType", "value": ""}}</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>{"status": 400, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>{"type": "object"}</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>["接口按Schema和业务规则接受或明确拒绝，不能产生500。"]</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Newman</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>TC_WEALTH_LEVEL_051_exception</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>获取财富等级经验及等级权益：query.deviceType 类型错误</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>exception</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>1.66666667</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>/level/exeperience/v2/get</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>regression, exception, exploratory</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "replace", "field": "query.deviceType", "value": 123456, "expected_type": "string", "exploratory_injection": {"field": "__debug", "value": true}}}</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>{"status": 400, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>{"type": "object"}</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>["接口返回参数错误，不产生500和业务脏数据。"]</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Newman</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>TC_WEALTH_LEVEL_052_boundary</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>获取财富等级经验及等级权益：query.deviceType minLength-1</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>boundary</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>0.45454545</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>/level/exeperience/v2/get</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>regression, boundary</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "replace", "field": "query.deviceType", "value": "", "boundary": "minLength-1"}}</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>{"status": 400, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>{"type": "object"}</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>["边界归属符合Schema；越界值被拒绝且不产生500。"]</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Newman</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>TC_WEALTH_LEVEL_053_boundary</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>获取财富等级经验及等级权益：query.deviceType minLength</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>boundary</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>0.45454545</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>/level/exeperience/v2/get</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>regression, boundary</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "replace", "field": "query.deviceType", "value": "a", "boundary": "minLength"}}</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>{"status": 400, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>{"type": "object"}</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>["边界归属符合Schema；越界值被拒绝且不产生500。"]</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Newman</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>TC_WEALTH_LEVEL_054_boundary</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>获取财富等级经验及等级权益：query.deviceType minLength+1</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>boundary</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>0.45454545</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>/level/exeperience/v2/get</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>regression, boundary</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "replace", "field": "query.deviceType", "value": "aa", "boundary": "minLength+1"}}</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>{"status": 400, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>{"type": "object"}</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>["边界归属符合Schema；越界值被拒绝且不产生500。"]</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Newman</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>TC_WEALTH_LEVEL_055_boundary</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>获取财富等级经验及等级权益：query.deviceType maxLength-1</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>boundary</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>0.45454545</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>/level/exeperience/v2/get</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>regression, boundary</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "replace", "field": "query.deviceType", "value": "aaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaa", "boundary": "maxLength-1"}}</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>{"status": 400, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>{"type": "object"}</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>["边界归属符合Schema；越界值被拒绝且不产生500。"]</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Newman</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>TC_WEALTH_LEVEL_056_boundary</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>获取财富等级经验及等级权益：query.deviceType maxLength</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>boundary</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>0.45454545</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>/level/exeperience/v2/get</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>regression, boundary</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "replace", "field": "query.deviceType", "value": "aaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaa", "boundary": "maxLength"}}</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>{"status": 400, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>{"type": "object"}</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>["边界归属符合Schema；越界值被拒绝且不产生500。"]</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Newman</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>TC_WEALTH_LEVEL_057_boundary</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>获取财富等级经验及等级权益：query.deviceType maxLength+1</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>boundary</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>0.45454545</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>/level/exeperience/v2/get</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>regression, boundary</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "replace", "field": "query.deviceType", "value": "aaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaa", "boundary": "maxLength+1"}}</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>{"status": 400, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>{"type": "object"}</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>["边界归属符合Schema；越界值被拒绝且不产生500。"]</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Newman</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>TC_WEALTH_LEVEL_058_exception</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>获取财富等级经验及等级权益：空请求或空参数</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>exception</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>1.66666667</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>/level/exeperience/v2/get</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>critical</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>regression, exception, critical, exploratory</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "empty_request", "exploratory_injection": {"field": "__debug", "value": true}}}</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>{"status": 400, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>{"type": "object"}</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>["返回400或明确的参数缺失错误，不产生500和部分业务写入。"]</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Newman</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>TC_WEALTH_LEVEL_059_exception</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>获取财富等级经验及等级权益：通用类型混淆</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>exception</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>1.66666667</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>/level/exeperience/v2/get</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>critical</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>regression, exception, critical</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "type_confusion", "field": "query.ticket", "value": 123456, "expected_type": "string"}}</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>{"status": 400, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>{"type": "object"}</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>["字符串、数字或布尔类型混淆时应返回明确参数错误。"]</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Newman</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>TC_WEALTH_LEVEL_060_boundary</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>获取财富等级经验及等级权益：单字段1MB超大Payload</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>boundary</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>0.45454545</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>/level/exeperience/v2/get</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>regression, boundary</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "oversized_payload", "field": "query.uid", "size_bytes": 1048576}}</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>{"status": 413, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>{"type": "object"}</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>["返回413、明确拒绝或受控截断，不进入正常业务写入。"]</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>pytest</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>REVIEW_REQUIRED</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>TC_WEALTH_LEVEL_061_exception</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>获取财富等级经验及等级权益：通用SQL注入检测</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>exception</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>1.66666667</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>/level/exeperience/v2/get</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>critical</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>regression, exception, critical, security</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "sql_injection", "field": "query.uid", "value": "' OR '1'='1"}}</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>{"status": 400, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>{"type": "object"}</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>["输入被安全转义或拒绝，不返回额外数据和数据库错误。"]</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>pytest</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>REVIEW_REQUIRED</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>TC_WEALTH_LEVEL_062_exception</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>获取财富等级经验及等级权益：通用XSS检测</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>exception</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>1.66666667</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>/level/exeperience/v2/get</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>regression, exception, security</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "xss_injection", "field": "query.uid", "value": "&lt;script&gt;alert(1)&lt;/script&gt;"}}</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>{"status": 400, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>{"type": "object"}</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>["脚本内容被转义或拒绝，不在响应或后续页面执行。"]</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>pytest</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>REVIEW_REQUIRED</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>TC_WEALTH_LEVEL_063_exception</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>获取财富等级经验及等级权益：Unicode空字符攻击</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>exception</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>1.66666667</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>/level/exeperience/v2/get</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>regression, exception, security</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "unicode_null", "field": "query.uid", "value": "prefix\u0000suffix"}}</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>{"status": 400, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>{"type": "object"}</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>["返回400或明确拒绝，不截断后绕过校验。"]</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>pytest</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>REVIEW_REQUIRED</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>TC_WEALTH_LEVEL_064_exception</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>获取财富等级经验及等级权益：路径遍历尝试</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>exception</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>1.66666667</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>/level/exeperience/v2/get</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>critical</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>regression, exception, critical, security</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "path_traversal", "field": "query.uid", "value": "../../../../etc/passwd"}}</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>{"status": 400, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>{"type": "object"}</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>["返回403、400或明确拒绝，不读取测试范围外文件。"]</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>pytest</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>REVIEW_REQUIRED</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>TC_WEALTH_LEVEL_065_boundary</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>获取财富等级经验及等级权益：超大ID越界</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>boundary</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>0.45454565</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>/level/exeperience/v2/get</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>regression, boundary</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "oversized_id", "field": "query.uid", "value": 999999999999999999999}}</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>{"status": 400, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>{"type": "object"}</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>["返回400或参数越界错误，不产生整数溢出和500。"]</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>pytest</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>REVIEW_REQUIRED</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>TC_WEALTH_LEVEL_066_exception</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>获取财富等级经验及等级权益：超时模拟</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>exception</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>1.66666667</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>/level/exeperience/v2/get</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>regression, exception, performance</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "timeout_simulation", "delay_ms": 30000}}</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>{"status": 504, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>{"type": "object"}</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>["存在受控延迟能力时返回504或明确超时；无注入能力时标记不适用并人工确认。"]</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>pytest</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>REVIEW_REQUIRED</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>TC_WEALTH_LEVEL_067_exception</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>获取财富等级经验及等级权益：缺失认证凭证</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>exception</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>1.66666667</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>/level/exeperience/v2/get</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>critical</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>regression, exception, critical</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "remove_auth"}}</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>{"status": 401, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>{"type": "object"}</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>["返回401或403，不返回受保护业务数据。"]</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Newman</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>TC_WEALTH_LEVEL_068_exception</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
           <t>获取财富等级经验及等级权益：无效或伪造认证凭证</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>测试环境可用
-准备接口所需身份与公共参数
-确认测试数据可恢复或只读</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>按请求变异规则准备数据
-发送 GET /level/exeperience/v2/get
-检查HTTP状态、业务码、响应Schema和业务数据</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>{"action": "replace_auth", "value": "invalid-token"}</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>返回401或403，不泄露凭证校验细节。</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>exception</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>1.66666667</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>/level/exeperience/v2/get</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>critical</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>regression, exception, critical</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "replace_auth", "value": "invalid-token"}}</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>{"status": 401, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>{"type": "object"}</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>["返回401或403，不泄露凭证校验细节。"]</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
         <is>
           <t>Newman</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="V69" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>STANDARD_TEST_ENVIRONMENT</t>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>TC_WEALTH_LEVEL_069_exception</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>获取财富等级经验及等级权益：重复提交与幂等性</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>exception</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>1.66666667</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>/level/exeperience/v2/get</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>critical</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>regression, exception, critical, performance</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "repeat_same_request", "times": 2}}</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>{"status": 400, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>{"type": "object"}</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>["相同幂等键重复请求不产生重复扣款、重复订单或重复状态流转；只读接口应返回一致结果。"]</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>pytest</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>REVIEW_REQUIRED</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>TC_WEALTH_LEVEL_070_exception</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>获取财富等级经验及等级权益：同一资源并发请求</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>exception</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>1.66666659</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>/level/exeperience/v2/get</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>critical</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>regression, exception, critical, performance</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>{"dependencies": [{"id": "DEP_AUTH", "description": "获取接口授权凭证", "source": "AUTH_PROVIDER", "extract": "$.data.token", "store_as": "{{auth_token}}", "on_fail": "skip_all", "inferred": true, "need_review": true}], "variables": {"query_ticket": "接口测试 Test data，正常值。", "query_uid": "接口测试 Test data，正常值。", "query_language": "接口测试 Test data，正常值。", "query_systemLanguage": "接口测试 Test data，正常值。", "query_appVersion": "接口测试 Test data，正常值。", "query_deviceType": "接口测试 Test data，正常值。", "auth_token": "{{runtime_auth_token}}"}}</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>{"path": {}, "query": {"ticket": "{{query_ticket}}", "uid": "{{query_uid}}", "language": "{{query_language}}", "systemLanguage": "{{query_systemLanguage}}", "appVersion": "{{query_appVersion}}", "deviceType": "{{query_deviceType}}"}, "headers": {}, "body": {}, "mutation": {"action": "concurrent_same_request", "users": 5}}</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>{"status": 400, "headers": ["Content-Type"], "version": "HTTP/1.1_or_HTTP/2"}</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>{"type": "object"}</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>["写接口应满足锁、版本和状态机约束；只读接口结果应稳定且无异常。"]</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>{"db": null, "cache": null, "message": null}</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>{"max_response_ms": 500}</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>{"action": "none", "on_fail": "ignore", "retry": 0, "timeout": 5000}</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>请核对推断约束和运行数据</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>JMeter</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
     </row>
